--- a/BCIO_data_extraction_template.xlsx
+++ b/BCIO_data_extraction_template.xlsx
@@ -2507,7 +2507,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
         </is>
       </c>
     </row>
@@ -3755,289 +3755,289 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:007017</t>
+          <t>BCIO:007302</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>monitoring BCT</t>
+          <t>suggest different perspective on behaviour BCT</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; that involves gathering or using information about performance.</t>
+          <t>A &lt;behaviour change technique&gt; that suggests the deliberate adoption of a new perspective on the behaviour.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:007022</t>
+          <t>BCIO:007053</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>provide feedback BCT</t>
+          <t>re-attribute cause BCT</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; in which feedback about the behaviour is provided.</t>
+          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves eliciting the person's beliefs about, and suggesting alternative beliefs about, the causes of the behaviour.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:007023</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>provide feedback on behaviour BCT</t>
+          <t>BCIO:007056</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>reframe past behaviour BCT</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>A &lt;provide feedback BCT&gt; that provides information about the person's previous performance of the behaviour.</t>
+          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves reattributing a person's successes to internal, stable or global factors or failures to external, unstable or specific factors.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:007027</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>provide feedback on outcome of behaviour BCT</t>
+          <t>BCIO:007057</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>draw attention to incompatible beliefs BCT</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>A &lt;provide feedback BCT&gt; that provides information about an outcome of the person's previous performance of the behaviour.</t>
+          <t>A &lt;suggest different perspective on behaviour BCT&gt; that draws the person's attention to the discrepancies between current or past behaviour and self-identity.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:007026</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>provide biofeedback BCT</t>
+          <t>BCIO:007052</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>inform about antecedents BCT</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>A &lt;provide feedback BCT&gt; that provides information about the functioning or state of the person's body, based on information collected by an external monitoring device.</t>
+          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves providing factual information to the person regarding triggers or influences that precede the initiation of the behaviour.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:007066</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>monitor emotional consequences BCT</t>
+          <t>BCIO:007017</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>monitoring BCT</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that involves the person assessing their emotions after performing the behaviour.</t>
+          <t>A &lt;behaviour change technique&gt; that involves gathering or using information about performance.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:007021</t>
+          <t>BCIO:007022</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>record outcome of behaviour without feedback BCT</t>
+          <t>provide feedback BCT</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that records an outcome of performing the behaviour with the person's knowledge but without providing feedback about the outcome.</t>
+          <t>A &lt;monitoring BCT&gt; in which feedback about the behaviour is provided.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:007018</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>observe behaviour without feedback BCT</t>
+          <t>BCIO:007023</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>provide feedback on behaviour BCT</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that observes current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
+          <t>A &lt;provide feedback BCT&gt; that provides information about the person's previous performance of the behaviour.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:007020</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>observe outcome of behaviour without feedback BCT</t>
+          <t>BCIO:007027</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>provide feedback on outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that observes an outcome of performing the behaviour with the person’s knowledge but without providing feedback about the outcome.</t>
+          <t>A &lt;provide feedback BCT&gt; that provides information about an outcome of the person's previous performance of the behaviour.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:007024</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>self-monitor behaviour BCT</t>
+          <t>BCIO:007026</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>provide biofeedback BCT</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record their behaviour.</t>
+          <t>A &lt;provide feedback BCT&gt; that provides information about the functioning or state of the person's body, based on information collected by an external monitoring device.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:007025</t>
+          <t>BCIO:007066</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>self-monitor outcome of behaviour BCT</t>
+          <t>monitor emotional consequences BCT</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record an outcome of their behaviour.</t>
+          <t>A &lt;monitoring BCT&gt; that involves the person assessing their emotions after performing the behaviour.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:007019</t>
+          <t>BCIO:007021</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>record behaviour without feedback BCT</t>
+          <t>record outcome of behaviour without feedback BCT</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that records current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
+          <t>A &lt;monitoring BCT&gt; that records an outcome of performing the behaviour with the person's knowledge but without providing feedback about the outcome.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:007302</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>suggest different perspective on behaviour BCT</t>
+          <t>BCIO:007018</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>observe behaviour without feedback BCT</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; that suggests the deliberate adoption of a new perspective on the behaviour.</t>
+          <t>A &lt;monitoring BCT&gt; that observes current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:007053</t>
+          <t>BCIO:007020</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>re-attribute cause BCT</t>
+          <t>observe outcome of behaviour without feedback BCT</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves eliciting the person's beliefs about, and suggesting alternative beliefs about, the causes of the behaviour.</t>
+          <t>A &lt;monitoring BCT&gt; that observes an outcome of performing the behaviour with the person’s knowledge but without providing feedback about the outcome.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:007056</t>
+          <t>BCIO:007024</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>reframe past behaviour BCT</t>
+          <t>self-monitor behaviour BCT</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves reattributing a person's successes to internal, stable or global factors or failures to external, unstable or specific factors.</t>
+          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record their behaviour.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:007057</t>
+          <t>BCIO:007025</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>draw attention to incompatible beliefs BCT</t>
+          <t>self-monitor outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>A &lt;suggest different perspective on behaviour BCT&gt; that draws the person's attention to the discrepancies between current or past behaviour and self-identity.</t>
+          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record an outcome of their behaviour.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:007052</t>
+          <t>BCIO:007019</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>inform about antecedents BCT</t>
+          <t>record behaviour without feedback BCT</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves providing factual information to the person regarding triggers or influences that precede the initiation of the behaviour.</t>
+          <t>A &lt;monitoring BCT&gt; that records current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
         </is>
       </c>
     </row>
@@ -4112,34 +4112,34 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:007299</t>
+          <t>BCIO:050445</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>review behaviour goal plan BCT</t>
+          <t>change behaviour goal BCT</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that reviews progress towards a behavioural goal and considers modifying the plan to achieve the goal.</t>
+          <t>A &lt;goal directed BCT&gt; that changes an existing goal for the behaviour to be achieved.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:050445</t>
+          <t>BCIO:007299</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>change behaviour goal BCT</t>
+          <t>review behaviour goal plan BCT</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that changes an existing goal for the behaviour to be achieved.</t>
+          <t>A &lt;goal directed BCT&gt; that reviews progress towards a behavioural goal and considers modifying the plan to achieve the goal.</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>realizable</t>
+          <t>realizable entity</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A disposition that inheres in some extended organism.</t>
+          <t>A bodily disposition is a disposition that inheres in some extended organism. Examples are: my disposition to catch a cold when exposed to a virus, my ability to speak the English language.</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
+          <t>A process in which at least one bodily component of an organsim participates.</t>
         </is>
       </c>
     </row>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
+          <t>A process in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
     </row>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>An affective process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
+          <t>An affective process that is a synchronized aggregate of constituent mental processes, including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
         </is>
       </c>
     </row>
@@ -13132,7 +13132,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Genuss</t>
+          <t>jouissance</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli</t>
+          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli. [Source: OCEAS]</t>
         </is>
       </c>
     </row>
@@ -13563,12 +13563,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>characteristic</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>A &lt;personal role&gt; that is realised in human social processes.</t>
+          <t>A personal role that is realised in human social processes.</t>
         </is>
       </c>
     </row>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>A &lt;personal role&gt; that is realised in a person by doing a specified type of work or working in a specified way.</t>
+          <t>A personal role that is realised in a person by doing a specified type of work or working in a specified way.</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>A bodily disposition that is realised as some behaviour.</t>
+          <t>A &lt;bodily disposition&gt; that is realised as some behaviour.</t>
         </is>
       </c>
     </row>
@@ -15076,7 +15076,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t xml:space="preserve">A mental disposition is a bodily disposition that is realized in a mental process. </t>
+          <t>A bodily disposition that is realized in a mental process.</t>
         </is>
       </c>
     </row>
@@ -19020,7 +19020,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>An &lt;emotional-relevance appraisal&gt; which represents a judgement about how avoidable the expected consequences of an event will be.</t>
+          <t>An affective appraisal which represents a judgement about how avoidable the expected consequences of an event will be.</t>
         </is>
       </c>
     </row>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>An appraisal that represents an evaluation that an event was caused by another person.</t>
+          <t>An &lt;appraisal of causal agency&gt; that represents an evaluation that an event was caused by another person.</t>
         </is>
       </c>
     </row>
@@ -19139,7 +19139,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>An appraisal that represents an evaluation that an event was caused by oneself.</t>
+          <t>An &lt;appraisal of causal agency&gt; that represents an evaluation that an event was caused by oneself.</t>
         </is>
       </c>
     </row>
@@ -19224,7 +19224,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>An affective appraisal that represents an evaluation of whether an event was expected to occur.</t>
+          <t>An &lt;emotional-relevance appraisal&gt; that represents an evaluation of whether an event was expected to occur.</t>
         </is>
       </c>
     </row>
@@ -19343,7 +19343,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>An &lt;identity&gt; that a person has about themselves.</t>
+          <t>An identity that a person has about themselves.</t>
         </is>
       </c>
     </row>
@@ -19360,7 +19360,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>A &lt;self-identity&gt; that represents a relation between oneself and another person or group</t>
+          <t>A self-identity that represents a relation between oneself and another person or group.</t>
         </is>
       </c>
     </row>
@@ -19632,7 +19632,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
@@ -20256,9 +20256,7 @@
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>Consciousness is an inseparable part of all mental processes. It is that part of the mental process that:
-a) confers a subjective perspective, a phenomenology, an experience of the mental process of which it is a part; and
-b) intends the object or event that the mental process is about, should such exist; i.e., it confers intentionality on the mental process.</t>
+          <t xml:space="preserve"> it confers intentionality on the mental process.</t>
         </is>
       </c>
     </row>
@@ -20360,7 +20358,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organism participates.</t>
+          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
     </row>
@@ -20377,7 +20375,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>A bodily process that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+          <t xml:space="preserve">Valence is a process profile of an emotion, mood, or affective bodily feeling (such as pleasure and pain). Valence can be positive or negative, with different strengths in both directions. For example, pleasure is positively valenced while pain is negatively valenced.  </t>
         </is>
       </c>
     </row>
@@ -20394,10 +20392,7 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>A mental process which is 
-a) produced by a causal process involving a part of the environment of the organism, and 
-b) is experienced by the organism as being so caused, and 
-c) in which the relevant part of the environment is thereby represented to the organism.</t>
+          <t>A &lt;mental process&gt; which is a) produced by a causal process involving a part of the environment of the organism, and b) is experienced by the organism as being so caused, and c) in which the relevant part of the environment is thereby represented to the organism.</t>
         </is>
       </c>
     </row>
@@ -20499,7 +20494,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t>A mental process that has positive or negative valence.</t>
+          <t xml:space="preserve">An affective process is any process that has positive or negative valence. </t>
         </is>
       </c>
     </row>
@@ -20511,12 +20506,12 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>subjective emotional feeling</t>
+          <t>subjective affective feeling</t>
         </is>
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>An affective process that involves the experience of internal or external sensory stimuli.</t>
+          <t>The subjective emotional feeling is that (fiat) part of the emotion process by which the organism experiences its own emotion.</t>
         </is>
       </c>
     </row>
@@ -20584,7 +20579,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>A &lt;subjective affective feeling&gt; of tiredness, needing sleep.</t>
+          <t>A subjective affective feeling of a need for sleep.</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20613,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>A &lt;subjective affective feeling&gt; of having lots of energy, being energetic.</t>
+          <t>A subjective affective feeling of having lots of energy, being energetic.</t>
         </is>
       </c>
     </row>
@@ -20720,9 +20715,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>A subjective affective feeling in an organism S, involving two integrated levels: 
-(a) activation of the nociceptive system and associated emotion generating brain components of S, and 
-(b) a simultaneous aversive sensory and emotional experience on the part of S, where (b) is phenomenologically similar to the sort of aversive experience involved in pain with concordant tissue damage.</t>
+          <t>A &lt;subjective affective feeling&gt; in an organism S, involving two integrated levels: (a) activation of the nociceptive system and associated emotion generating brain components of S, and (b) a simultaneous aversive sensory and emotional experience on the part of S, where (b) is phenomenologically similar to the sort of aversive experience involved in pain with concordant tissue damage.</t>
         </is>
       </c>
     </row>
@@ -20739,7 +20732,7 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>A subjective affective feeling that involves discomfort and is associated with a need to consume food.</t>
+          <t>A &lt;subjective affective feeling&gt; that involves discomfort and is associated with a need to consume food.</t>
         </is>
       </c>
     </row>
@@ -20824,7 +20817,7 @@
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>A subjective affective feeling that is a strong feeling of desire or a strong feeling of urge.</t>
+          <t>A &lt;subjective affective feeling&gt; involving a strong desire or urge.</t>
         </is>
       </c>
     </row>
@@ -20892,7 +20885,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>An &lt;affective process&gt; that is a synchronized aggregate of constituent mental processes, including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
+          <t>An affective process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
         </is>
       </c>
     </row>
@@ -21028,7 +21021,7 @@
       </c>
       <c r="O445" t="inlineStr">
         <is>
-          <t>A positive emotion which is experienced in reaction to a positive experience or event.</t>
+          <t>A positive emotion which is experienced in reaction to a positive experience or event. [Source: OCEAS]</t>
         </is>
       </c>
     </row>
@@ -21045,7 +21038,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>Satisfaction is an emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
+          <t>An emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
         </is>
       </c>
     </row>
@@ -21147,7 +21140,7 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t>&lt;Disgust&gt; elicited by contact with others, especially contact with strangers or other individuals or groups we are averse to.</t>
+          <t>Disgust elicited by contact with others, especially contact with strangers or other individuals or groups we are averse to. [Source: OCEAS]</t>
         </is>
       </c>
     </row>
@@ -21164,7 +21157,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t>&lt;Disgust&gt; elicited by poor hygiene, inappropriate sex, gore or violations of bodily boundaries, and death or the odor of decay.</t>
+          <t>Disgust elicited by poor hygiene, inappropriate sex, gore or violations of bodily boundaries, and death or the odor of decay. [Source: OCEAS]</t>
         </is>
       </c>
     </row>
@@ -21181,7 +21174,8 @@
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t>A negative emotion, characterised by feelings of unpleasantness and high arousal, in the form of antagonistic feelings and action tendencies.</t>
+          <t xml:space="preserve">Anger is a negative emotion, characterised by feelings of unpleasantness and high arousal, in the form of antagonistic feelings and action tendencies. [Source: OCEAS]
+</t>
         </is>
       </c>
     </row>
@@ -21334,7 +21328,7 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>&lt;Pleasure&gt; that is experienced as a result of sexual activities.</t>
+          <t>Pleasure that is experienced as a result of sexual activities.</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21362,7 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t>A mental process that is the psychological and physiological state of being awake and reactive to stimuli.</t>
+          <t>A &lt;mental process&gt; that involves heightened responding to an internal or external stimulus.</t>
         </is>
       </c>
     </row>
@@ -21402,7 +21396,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>the process whereby relevant aspects of our mental experience are focused on specific targets</t>
+          <t>A &lt;mental process&gt; whereby relevant aspects of one's mental experience are focused on specific targets.</t>
         </is>
       </c>
     </row>
@@ -21470,7 +21464,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>a mental process that involves the manipulation of mental language and/or mental images</t>
+          <t>A &lt;cognitive process&gt; that involves the manipulation of mental language and/or mental images.</t>
         </is>
       </c>
     </row>
@@ -21827,7 +21821,7 @@
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t>A &lt;mental process&gt; that evokes the representation of the sensory characteristics of objects or events when these are not immediately present to the senses.</t>
+          <t>A mental process that evokes the representation of the sensory characteristics of objects or events when these are not immediately present to the senses.</t>
         </is>
       </c>
     </row>
@@ -21895,7 +21889,7 @@
       </c>
       <c r="O496" t="inlineStr">
         <is>
-          <t>A decrease in a behavioral response to a repeated stimulus. This is exemplified by the failure of a person to show a startle response to a loud noise that has been repeatedly presented.</t>
+          <t>A decrease in a behavioural response to a repeated stimulus.</t>
         </is>
       </c>
     </row>
@@ -22133,7 +22127,7 @@
       </c>
       <c r="O510" t="inlineStr">
         <is>
-          <t>Learning in which new behaviors are acquired through imitation.</t>
+          <t>&lt;Observational learning&gt; in which new behaviours are acquired through imitation.</t>
         </is>
       </c>
     </row>
@@ -22745,7 +22739,7 @@
       </c>
       <c r="O546" t="inlineStr">
         <is>
-          <t>A mental process that involves thinking about a state of affairs that is not yet the case together with a desire for that state of affairs to come about.</t>
+          <t>A &lt;mental process&gt; that involves thinking about a state of affairs that is not yet the case together with a desire for that state of affairs to come about.</t>
         </is>
       </c>
     </row>
@@ -22779,7 +22773,7 @@
       </c>
       <c r="O548" t="inlineStr">
         <is>
-          <t>A &lt;mental process&gt; that involves neuronal activity in response to a sensory stimulus but which is not the subject of consciousness.</t>
+          <t>A mental process that involves neuronal activity in response to a sensory stimuli but which is not the subject of consciousness.</t>
         </is>
       </c>
     </row>
@@ -23119,7 +23113,7 @@
       </c>
       <c r="O568" t="inlineStr">
         <is>
-          <t>A &lt;mental process&gt; that gives rise to an appraisal.</t>
+          <t>A mental process that gives rise to an appraisal.</t>
         </is>
       </c>
     </row>
@@ -23527,7 +23521,7 @@
       </c>
       <c r="O592" t="inlineStr">
         <is>
-          <t>An individual human behaviour that relates to the social environment.</t>
+          <t>An &lt;individual human behaviour&gt; that relates to the social environment.</t>
         </is>
       </c>
     </row>
@@ -23595,7 +23589,7 @@
       </c>
       <c r="O596" t="inlineStr">
         <is>
-          <t>A human communication behaviour in which information is transmitted without being encoded in the meaning units of any language.</t>
+          <t>A &lt;human communication behaviour&gt; in which information is transmitted without being encoded in the meaning units of any language.</t>
         </is>
       </c>
     </row>
@@ -23748,7 +23742,7 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>An &lt;individual human behaviour&gt; that conveys a thought or feeling.</t>
+          <t>An individual human behaviour that conveys a thought or feeling.</t>
         </is>
       </c>
     </row>
@@ -26586,136 +26580,136 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:015839</t>
+          <t>BCIO:015791</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>socioeconomic position score population statistic</t>
+          <t>unpaid carer for an adult status population statistic</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A population statistic about socioeconomic position score.</t>
+          <t>A population statistic about unpaid carer for an adult status.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:015840</t>
+          <t>BCIO:015793</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>mean socioeconomic position score population statistic</t>
+          <t>proportion unpaid carer for an adult status population statistic</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A(n) socioeconomic position score population statistic that is the mean value of socioeconomic position score in the population.</t>
+          <t>A(n) unpaid carer for an adult status population statistic that is the proportion of people that have unpaid carer for an adult status in the population.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:015842</t>
+          <t>BCIO:015792</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>maximum socioeconomic position score population statistic</t>
+          <t>percentage unpaid carer for an adult status population statistic</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A(n) socioeconomic position score population statistic that is the maximum value of socioeconomic position score in the population.</t>
+          <t>A(n) unpaid carer for an adult status population statistic that is the percentage of people that have unpaid carer for an adult status in the population.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:015843</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>median socioeconomic position score population statistic</t>
+          <t>BCIO:015839</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>socioeconomic position score population statistic</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>A(n) socioeconomic position score population statistic that is the median value of socioeconomic position score in the population.</t>
+          <t>A population statistic about socioeconomic position score.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:015841</t>
+          <t>BCIO:015840</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>minimum socioeconomic position score population statistic</t>
+          <t>mean socioeconomic position score population statistic</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>A(n) socioeconomic position score population statistic that is the minimum value of socioeconomic position score in the population.</t>
+          <t>A(n) socioeconomic position score population statistic that is the mean value of socioeconomic position score in the population.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:015791</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>unpaid carer for an adult status population statistic</t>
+          <t>BCIO:015842</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>maximum socioeconomic position score population statistic</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>A population statistic about unpaid carer for an adult status.</t>
+          <t>A(n) socioeconomic position score population statistic that is the maximum value of socioeconomic position score in the population.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:015793</t>
+          <t>BCIO:015843</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>proportion unpaid carer for an adult status population statistic</t>
+          <t>median socioeconomic position score population statistic</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>A(n) unpaid carer for an adult status population statistic that is the proportion of people that have unpaid carer for an adult status in the population.</t>
+          <t>A(n) socioeconomic position score population statistic that is the median value of socioeconomic position score in the population.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:015792</t>
+          <t>BCIO:015841</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>percentage unpaid carer for an adult status population statistic</t>
+          <t>minimum socioeconomic position score population statistic</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>A(n) unpaid carer for an adult status population statistic that is the percentage of people that have unpaid carer for an adult status in the population.</t>
+          <t>A(n) socioeconomic position score population statistic that is the minimum value of socioeconomic position score in the population.</t>
         </is>
       </c>
     </row>
@@ -26841,153 +26835,153 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:015821</t>
+          <t>BCIO:015816</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>proportion behavioural frequency population statistic</t>
+          <t>mean behavioural frequency population statistic</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>A(n) behavioural frequency population statistic that is the proportion of individuals having a behavioural frequency in the population.</t>
+          <t>A(n) behavioural frequency population statistic that is the mean value of behavioural frequency in the population.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:015829</t>
+          <t>BCIO:015821</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>frequency of past behaviour population statistic</t>
+          <t>proportion behavioural frequency population statistic</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>A population statistic about frequency of past behaviour.</t>
+          <t>A(n) behavioural frequency population statistic that is the proportion of individuals having a behavioural frequency in the population.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:015833</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>median frequency of past behaviour population statistic</t>
+          <t>BCIO:015829</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>frequency of past behaviour population statistic</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>A(n) frequency of past behaviour population statistic that is the median value of frequency of past behaviour in the population.</t>
+          <t>A population statistic about frequency of past behaviour.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:015831</t>
+          <t>BCIO:015833</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>minimum frequency of past behaviour population statistic</t>
+          <t>median frequency of past behaviour population statistic</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>A(n) frequency of past behaviour population statistic that is the minimum value of frequency of past behaviour in the population.</t>
+          <t>A(n) frequency of past behaviour population statistic that is the median value of frequency of past behaviour in the population.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:015830</t>
+          <t>BCIO:015831</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>mean frequency of past behaviour population statistic</t>
+          <t>minimum frequency of past behaviour population statistic</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>A(n) frequency of past behaviour population statistic that is the mean value of frequency of past behaviour in the population.</t>
+          <t>A(n) frequency of past behaviour population statistic that is the minimum value of frequency of past behaviour in the population.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:015835</t>
+          <t>BCIO:015830</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>proportion frequency of past behaviour population statistic</t>
+          <t>mean frequency of past behaviour population statistic</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>A(n) frequency of past behaviour population statistic that is the proportion of individuals having a frequency of past behaviour in the population.</t>
+          <t>A(n) frequency of past behaviour population statistic that is the mean value of frequency of past behaviour in the population.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:015834</t>
+          <t>BCIO:015835</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>percentage frequency of past behaviour population statistic</t>
+          <t>proportion frequency of past behaviour population statistic</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>A(n) frequency of past behaviour population statistic that is the percentage value of frequency of past behaviour in the population.</t>
+          <t>A(n) frequency of past behaviour population statistic that is the proportion of individuals having a frequency of past behaviour in the population.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:015832</t>
+          <t>BCIO:015834</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>maximum frequency of past behaviour population statistic</t>
+          <t>percentage frequency of past behaviour population statistic</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>A(n) frequency of past behaviour population statistic that is the maximum value of frequency of past behaviour in the population.</t>
+          <t>A(n) frequency of past behaviour population statistic that is the percentage value of frequency of past behaviour in the population.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:015816</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>mean behavioural frequency population statistic</t>
+          <t>BCIO:015832</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>maximum frequency of past behaviour population statistic</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>A(n) behavioural frequency population statistic that is the mean value of behavioural frequency in the population.</t>
+          <t>A(n) frequency of past behaviour population statistic that is the maximum value of frequency of past behaviour in the population.</t>
         </is>
       </c>
     </row>
@@ -28694,34 +28688,34 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BCIO:015771</t>
+          <t>BCIO:015772</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>percentage transgender population statistic</t>
+          <t>proportion transgender population statistic</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>A(n) transgender population statistic that is the percentage of people that are transgender in the population.</t>
+          <t>A(n) transgender population statistic that is the proportion of people that are transgender in the population.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:015772</t>
+          <t>BCIO:015771</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>proportion transgender population statistic</t>
+          <t>percentage transgender population statistic</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>A(n) transgender population statistic that is the proportion of people that are transgender in the population.</t>
+          <t>A(n) transgender population statistic that is the percentage of people that are transgender in the population.</t>
         </is>
       </c>
     </row>
@@ -31006,51 +31000,51 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>BCIO:015546</t>
+          <t>BCIO:015420</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>not seeking employment population statistic</t>
+          <t>immigrant population statistic</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>A population statistic about not seeking employment.</t>
+          <t>A population statistic about immigrant.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>BCIO:015548</t>
+          <t>BCIO:015421</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>proportion not seeking employment population statistic</t>
+          <t>percentage immigrant population statistic</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>A(n) not seeking employment population statistic that is the proportion of people that are not seeking employment in the population.</t>
+          <t>A(n) immigrant population statistic that is the percentage of people that are a immigrant in the population.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>BCIO:015547</t>
+          <t>BCIO:015422</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>percentage not seeking employment population statistic</t>
+          <t>proportion immigrant population statistic</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>A(n) not seeking employment population statistic that is the percentage of people that are not seeking employment in the population.</t>
+          <t>A(n) immigrant population statistic that is the proportion of people that are a immigrant in the population.</t>
         </is>
       </c>
     </row>
@@ -31312,714 +31306,714 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>BCIO:015420</t>
+          <t>BCIO:015249</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>immigrant population statistic</t>
+          <t>biological sex population statistic</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>A population statistic about immigrant.</t>
+          <t>A population statistic about biological sex.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>BCIO:015421</t>
+          <t>BCIO:015327</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>percentage immigrant population statistic</t>
+          <t>female biological sex population statistic</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>A(n) immigrant population statistic that is the percentage of people that are a immigrant in the population.</t>
+          <t>A population statistic about female biological sex.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>BCIO:015422</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>proportion immigrant population statistic</t>
+          <t>BCIO:015329</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>proportion female biological sex population statistic</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>A(n) immigrant population statistic that is the proportion of people that are a immigrant in the population.</t>
+          <t>A(n) female biological sex population statistic that is the proportion of people that have a female biological sex in the population.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>BCIO:015249</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>biological sex population statistic</t>
+          <t>BCIO:015328</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>percentage female biological sex population statistic</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>A population statistic about biological sex.</t>
+          <t>A(n) female biological sex population statistic that is the percentage of people that have a female biological sex in the population.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>BCIO:015327</t>
+          <t>BCIO:015251</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>female biological sex population statistic</t>
+          <t>proportion biological sex population statistic</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>A population statistic about female biological sex.</t>
+          <t>A(n) biological sex population statistic that is the proportion of people that have a biological sex in the population.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>BCIO:015329</t>
-        </is>
-      </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t>proportion female biological sex population statistic</t>
+          <t>BCIO:015250</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>percentage biological sex population statistic</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>A(n) female biological sex population statistic that is the proportion of people that have a female biological sex in the population.</t>
+          <t>A(n) biological sex population statistic that is the percentage of people that have a biological sex in the population.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>BCIO:015328</t>
-        </is>
-      </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>percentage female biological sex population statistic</t>
+          <t>BCIO:015494</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>male biological sex population statistic</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>A(n) female biological sex population statistic that is the percentage of people that have a female biological sex in the population.</t>
+          <t>A population statistic about male biological sex.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>BCIO:015251</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>proportion biological sex population statistic</t>
+          <t>BCIO:015496</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>proportion male biological sex population statistic</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>A(n) biological sex population statistic that is the proportion of people that have a biological sex in the population.</t>
+          <t>A(n) male biological sex population statistic that is the proportion of people that have a male biological sex in the population.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>BCIO:015250</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>percentage biological sex population statistic</t>
+          <t>BCIO:015495</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>percentage male biological sex population statistic</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>A(n) biological sex population statistic that is the percentage of people that have a biological sex in the population.</t>
+          <t>A(n) male biological sex population statistic that is the percentage of people that have a male biological sex in the population.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>BCIO:015494</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>male biological sex population statistic</t>
+          <t>BCIO:015312</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>employment status population statistic</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>A population statistic about male biological sex.</t>
+          <t>A population statistic about employment status.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>BCIO:015496</t>
-        </is>
-      </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t>proportion male biological sex population statistic</t>
+          <t>BCIO:015714</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>self employed status population statistic</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>A(n) male biological sex population statistic that is the proportion of people that have a male biological sex in the population.</t>
+          <t>A population statistic about self employed status.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>BCIO:015495</t>
+          <t>BCIO:015715</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>percentage male biological sex population statistic</t>
+          <t>percentage self employed status population statistic</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>A(n) male biological sex population statistic that is the percentage of people that have a male biological sex in the population.</t>
+          <t>A(n) self employed status population statistic that is the percentage of people that have self employed status in the population.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>BCIO:015312</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>employment status population statistic</t>
+          <t>BCIO:015716</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>proportion self employed status population statistic</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>A population statistic about employment status.</t>
+          <t>A(n) self employed status population statistic that is the proportion of people that have self employed status in the population.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>BCIO:015714</t>
+          <t>BCIO:015300</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>self employed status population statistic</t>
+          <t>employed population statistic</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>A population statistic about self employed status.</t>
+          <t>A population statistic about employed.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>BCIO:015715</t>
+          <t>BCIO:015301</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>percentage self employed status population statistic</t>
+          <t>percentage employed population statistic</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>A(n) self employed status population statistic that is the percentage of people that have self employed status in the population.</t>
+          <t>A(n) employed population statistic that is the percentage of people that are employed in the population.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>BCIO:015716</t>
+          <t>BCIO:015302</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>proportion self employed status population statistic</t>
+          <t>proportion employed population statistic</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>A(n) self employed status population statistic that is the proportion of people that have self employed status in the population.</t>
+          <t>A(n) employed population statistic that is the proportion of people that are employed in the population.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>BCIO:015300</t>
+          <t>BCIO:015313</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>employed population statistic</t>
+          <t>percentage employment status population statistic</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>A population statistic about employed.</t>
+          <t>A(n) employment status population statistic that is the percentage of people that have a employment status in the population.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>BCIO:015301</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>percentage employed population statistic</t>
+          <t>BCIO:015429</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>in permanent employment population statistic</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>A(n) employed population statistic that is the percentage of people that are employed in the population.</t>
+          <t>A population statistic about in permanent employment.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>BCIO:015302</t>
+          <t>BCIO:015431</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>proportion employed population statistic</t>
+          <t>percentage in permanent employment population statistic</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>A(n) employed population statistic that is the proportion of people that are employed in the population.</t>
+          <t>A(n) in permanent employment population statistic that is the percentage of people that are in permanent employment in the population.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>BCIO:015313</t>
-        </is>
-      </c>
-      <c r="I320" t="inlineStr">
-        <is>
-          <t>percentage employment status population statistic</t>
+          <t>BCIO:015432</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>proportion in permanent employment population statistic</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>A(n) employment status population statistic that is the percentage of people that have a employment status in the population.</t>
+          <t>A(n) in permanent employment population statistic that is the proportion of people that are in permanent employment in the population.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>BCIO:015429</t>
+          <t>BCIO:015306</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>in permanent employment population statistic</t>
+          <t>employed in shift work population statistic</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>A population statistic about in permanent employment.</t>
+          <t>A population statistic about employed in shift work.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>BCIO:015431</t>
+          <t>BCIO:015308</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>percentage in permanent employment population statistic</t>
+          <t>proportion employed in shift work population statistic</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>A(n) in permanent employment population statistic that is the percentage of people that are in permanent employment in the population.</t>
+          <t>A(n) employed in shift work population statistic that is the proportion of people that are employed in shift work in the population.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>BCIO:015432</t>
+          <t>BCIO:015307</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>proportion in permanent employment population statistic</t>
+          <t>percentage employed in shift work population statistic</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>A(n) in permanent employment population statistic that is the proportion of people that are in permanent employment in the population.</t>
+          <t>A(n) employed in shift work population statistic that is the percentage of people that are employed in shift work in the population.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>BCIO:015306</t>
+          <t>BCIO:015433</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>employed in shift work population statistic</t>
+          <t>in short term or temporary employment with known conditions population statistic</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>A population statistic about employed in shift work.</t>
+          <t>A population statistic about in short term or temporary employment with known conditions.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>BCIO:015308</t>
+          <t>BCIO:015434</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>proportion employed in shift work population statistic</t>
+          <t>percentage in short term or temporary employment with known conditions population statistic</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>A(n) employed in shift work population statistic that is the proportion of people that are employed in shift work in the population.</t>
+          <t>A(n) in short term or temporary employment with known conditions population statistic that is the percentage of people that are in short term or temporary employment with known conditions in the population.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>BCIO:015307</t>
+          <t>BCIO:015435</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>percentage employed in shift work population statistic</t>
+          <t>proportion in short term or temporary employment with known conditions population statistic</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>A(n) employed in shift work population statistic that is the percentage of people that are employed in shift work in the population.</t>
+          <t>A(n) in short term or temporary employment with known conditions population statistic that is the proportion of people that are in short term or temporary employment with known conditions in the population.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>BCIO:015433</t>
+          <t>BCIO:015314</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>in short term or temporary employment with known conditions population statistic</t>
+          <t>proportion employment status population statistic</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>A population statistic about in short term or temporary employment with known conditions.</t>
+          <t>A(n) employment status population statistic that is the proportion of people that have a employment status in the population.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>BCIO:015434</t>
-        </is>
-      </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>percentage in short term or temporary employment with known conditions population statistic</t>
+          <t>BCIO:015436</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>in uncertain employment population statistic</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>A(n) in short term or temporary employment with known conditions population statistic that is the percentage of people that are in short term or temporary employment with known conditions in the population.</t>
+          <t>A population statistic about in uncertain employment.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>BCIO:015435</t>
+          <t>BCIO:015438</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>proportion in short term or temporary employment with known conditions population statistic</t>
+          <t>proportion in uncertain employment population statistic</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>A(n) in short term or temporary employment with known conditions population statistic that is the proportion of people that are in short term or temporary employment with known conditions in the population.</t>
+          <t>A(n) in uncertain employment population statistic that is the proportion of people that are in uncertain employment in the population.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>BCIO:015314</t>
-        </is>
-      </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>proportion employment status population statistic</t>
+          <t>BCIO:015437</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>percentage in uncertain employment population statistic</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>A(n) employment status population statistic that is the proportion of people that have a employment status in the population.</t>
+          <t>A(n) in uncertain employment population statistic that is the percentage of people that are in uncertain employment in the population.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>BCIO:015436</t>
+          <t>BCIO:015303</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>in uncertain employment population statistic</t>
+          <t>employed full time population statistic</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>A population statistic about in uncertain employment.</t>
+          <t>A population statistic about employed full time.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>BCIO:015437</t>
+          <t>BCIO:015305</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>percentage in uncertain employment population statistic</t>
+          <t>proportion employed full time population statistic</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>A(n) in uncertain employment population statistic that is the percentage of people that are in uncertain employment in the population.</t>
+          <t>A(n) employed full time population statistic that is the proportion of people that are employed full time in the population.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>BCIO:015438</t>
+          <t>BCIO:015304</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>proportion in uncertain employment population statistic</t>
+          <t>percentage employed full time population statistic</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>A(n) in uncertain employment population statistic that is the proportion of people that are in uncertain employment in the population.</t>
+          <t>A(n) employed full time population statistic that is the percentage of people that are employed full time in the population.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>BCIO:015303</t>
+          <t>BCIO:015788</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>employed full time population statistic</t>
+          <t>unemployed population statistic</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>A population statistic about employed full time.</t>
+          <t>A population statistic about unemployed.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>BCIO:015305</t>
+          <t>BCIO:015790</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>proportion employed full time population statistic</t>
+          <t>proportion unemployed population statistic</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>A(n) employed full time population statistic that is the proportion of people that are employed full time in the population.</t>
+          <t>A(n) unemployed population statistic that is the proportion of people that are unemployed in the population.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>BCIO:015304</t>
+          <t>BCIO:015789</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>percentage employed full time population statistic</t>
+          <t>percentage unemployed population statistic</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>A(n) employed full time population statistic that is the percentage of people that are employed full time in the population.</t>
+          <t>A(n) unemployed population statistic that is the percentage of people that are unemployed in the population.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>BCIO:015788</t>
+          <t>BCIO:015309</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>unemployed population statistic</t>
+          <t>employed part time population statistic</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>A population statistic about unemployed.</t>
+          <t>A population statistic about employed part time.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>BCIO:015790</t>
+          <t>BCIO:015311</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>proportion unemployed population statistic</t>
+          <t>proportion employed part time population statistic</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>A(n) unemployed population statistic that is the proportion of people that are unemployed in the population.</t>
+          <t>A(n) employed part time population statistic that is the proportion of people that are employed part time in the population.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>BCIO:015789</t>
+          <t>BCIO:015310</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>percentage unemployed population statistic</t>
+          <t>percentage employed part time population statistic</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>A(n) unemployed population statistic that is the percentage of people that are unemployed in the population.</t>
+          <t>A(n) employed part time population statistic that is the percentage of people that are employed part time in the population.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>BCIO:015309</t>
-        </is>
-      </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>employed part time population statistic</t>
+          <t>BCIO:015546</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>not seeking employment population statistic</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>A population statistic about employed part time.</t>
+          <t>A population statistic about not seeking employment.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>BCIO:015311</t>
-        </is>
-      </c>
-      <c r="J341" t="inlineStr">
-        <is>
-          <t>proportion employed part time population statistic</t>
+          <t>BCIO:015548</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>proportion not seeking employment population statistic</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>A(n) employed part time population statistic that is the proportion of people that are employed part time in the population.</t>
+          <t>A(n) not seeking employment population statistic that is the proportion of people that are not seeking employment in the population.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>BCIO:015310</t>
-        </is>
-      </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>percentage employed part time population statistic</t>
+          <t>BCIO:015547</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>percentage not seeking employment population statistic</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>A(n) employed part time population statistic that is the percentage of people that are employed part time in the population.</t>
+          <t>A(n) not seeking employment population statistic that is the percentage of people that are not seeking employment in the population.</t>
         </is>
       </c>
     </row>
@@ -34185,68 +34179,68 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>BCIO:015656</t>
+          <t>BCIO:015651</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>proportion personal vulnerability to harmful behaviour population statistic</t>
+          <t>mean personal vulnerability to harmful behaviour population statistic</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the proportion of individuals having a personal vulnerability to harmful behaviour in the population.</t>
+          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the mean value of personal vulnerability to harmful behaviour in the population.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>BCIO:015653</t>
+          <t>BCIO:015656</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>maximum personal vulnerability to harmful behaviour population statistic</t>
+          <t>proportion personal vulnerability to harmful behaviour population statistic</t>
         </is>
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the maximum value of personal vulnerability to harmful behaviour in the population.</t>
+          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the proportion of individuals having a personal vulnerability to harmful behaviour in the population.</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>BCIO:015654</t>
+          <t>BCIO:015653</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>median personal vulnerability to harmful behaviour population statistic</t>
+          <t>maximum personal vulnerability to harmful behaviour population statistic</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the median value of personal vulnerability to harmful behaviour in the population.</t>
+          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the maximum value of personal vulnerability to harmful behaviour in the population.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>BCIO:015651</t>
+          <t>BCIO:015654</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>mean personal vulnerability to harmful behaviour population statistic</t>
+          <t>median personal vulnerability to harmful behaviour population statistic</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the mean value of personal vulnerability to harmful behaviour in the population.</t>
+          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the median value of personal vulnerability to harmful behaviour in the population.</t>
         </is>
       </c>
     </row>
@@ -34287,34 +34281,34 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>BCIO:015648</t>
+          <t>BCIO:015649</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>percentage personal vulnerability population statistic</t>
+          <t>proportion personal vulnerability population statistic</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability population statistic that is the percentage value of personal vulnerability in the population.</t>
+          <t>A(n) personal vulnerability population statistic that is the proportion of individuals having a personal vulnerability in the population.</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>BCIO:015649</t>
+          <t>BCIO:015648</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>proportion personal vulnerability population statistic</t>
+          <t>percentage personal vulnerability population statistic</t>
         </is>
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability population statistic that is the proportion of individuals having a personal vulnerability in the population.</t>
+          <t>A(n) personal vulnerability population statistic that is the percentage value of personal vulnerability in the population.</t>
         </is>
       </c>
     </row>
@@ -34474,170 +34468,170 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>BCIO:015279</t>
+          <t>BCIO:015594</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>country of birth population statistic</t>
+          <t>personal history of behavioural lapse population statistic</t>
         </is>
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>A population statistic about country of birth.</t>
+          <t>A population statistic about personal history of behavioural lapse.</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>BCIO:015280</t>
+          <t>BCIO:015595</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>percentage country of birth population statistic</t>
+          <t>mean personal history of behavioural lapse population statistic</t>
         </is>
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>A(n) country of birth population statistic that is the percentage of people that have a country of birth in the population.</t>
+          <t>A(n) personal history of behavioural lapse population statistic that is the mean value of personal history of behavioural lapse in the population.</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>BCIO:015281</t>
+          <t>BCIO:015598</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>proportion country of birth population statistic</t>
+          <t>median personal history of behavioural lapse population statistic</t>
         </is>
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>A(n) country of birth population statistic that is the proportion of people that have a country of birth in the population.</t>
+          <t>A(n) personal history of behavioural lapse population statistic that is the median value of personal history of behavioural lapse in the population.</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>BCIO:015594</t>
-        </is>
-      </c>
-      <c r="H490" t="inlineStr">
-        <is>
-          <t>personal history of behavioural lapse population statistic</t>
+          <t>BCIO:015597</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>maximum personal history of behavioural lapse population statistic</t>
         </is>
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>A population statistic about personal history of behavioural lapse.</t>
+          <t>A(n) personal history of behavioural lapse population statistic that is the maximum value of personal history of behavioural lapse in the population.</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>BCIO:015595</t>
+          <t>BCIO:015596</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>mean personal history of behavioural lapse population statistic</t>
+          <t>minimum personal history of behavioural lapse population statistic</t>
         </is>
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>A(n) personal history of behavioural lapse population statistic that is the mean value of personal history of behavioural lapse in the population.</t>
+          <t>A(n) personal history of behavioural lapse population statistic that is the minimum value of personal history of behavioural lapse in the population.</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>BCIO:015598</t>
+          <t>BCIO:015599</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>median personal history of behavioural lapse population statistic</t>
+          <t>percentage personal history of behavioural lapse population statistic</t>
         </is>
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>A(n) personal history of behavioural lapse population statistic that is the median value of personal history of behavioural lapse in the population.</t>
+          <t>A(n) personal history of behavioural lapse population statistic that is the percentage value of personal history of behavioural lapse in the population.</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>BCIO:015597</t>
+          <t>BCIO:015600</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>maximum personal history of behavioural lapse population statistic</t>
+          <t>proportion personal history of behavioural lapse population statistic</t>
         </is>
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>A(n) personal history of behavioural lapse population statistic that is the maximum value of personal history of behavioural lapse in the population.</t>
+          <t>A(n) personal history of behavioural lapse population statistic that is the proportion of individuals having a personal history of behavioural lapse in the population.</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>BCIO:015596</t>
-        </is>
-      </c>
-      <c r="I494" t="inlineStr">
-        <is>
-          <t>minimum personal history of behavioural lapse population statistic</t>
+          <t>BCIO:015279</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>country of birth population statistic</t>
         </is>
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>A(n) personal history of behavioural lapse population statistic that is the minimum value of personal history of behavioural lapse in the population.</t>
+          <t>A population statistic about country of birth.</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>BCIO:015599</t>
+          <t>BCIO:015280</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>percentage personal history of behavioural lapse population statistic</t>
+          <t>percentage country of birth population statistic</t>
         </is>
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>A(n) personal history of behavioural lapse population statistic that is the percentage value of personal history of behavioural lapse in the population.</t>
+          <t>A(n) country of birth population statistic that is the percentage of people that have a country of birth in the population.</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>BCIO:015600</t>
+          <t>BCIO:015281</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>proportion personal history of behavioural lapse population statistic</t>
+          <t>proportion country of birth population statistic</t>
         </is>
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>A(n) personal history of behavioural lapse population statistic that is the proportion of individuals having a personal history of behavioural lapse in the population.</t>
+          <t>A(n) country of birth population statistic that is the proportion of people that have a country of birth in the population.</t>
         </is>
       </c>
     </row>
@@ -35970,34 +35964,34 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>BCIO:015355</t>
+          <t>BCIO:015356</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
         <is>
-          <t>percentage foster sister population statistic</t>
+          <t>proportion foster sister population statistic</t>
         </is>
       </c>
       <c r="M575" t="inlineStr">
         <is>
-          <t>A(n) foster sister population statistic that is the percentage of people that are a foster sister in the population.</t>
+          <t>A(n) foster sister population statistic that is the proportion of people that are a foster sister in the population.</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>BCIO:015356</t>
+          <t>BCIO:015355</t>
         </is>
       </c>
       <c r="L576" t="inlineStr">
         <is>
-          <t>proportion foster sister population statistic</t>
+          <t>percentage foster sister population statistic</t>
         </is>
       </c>
       <c r="M576" t="inlineStr">
         <is>
-          <t>A(n) foster sister population statistic that is the proportion of people that are a foster sister in the population.</t>
+          <t>A(n) foster sister population statistic that is the percentage of people that are a foster sister in the population.</t>
         </is>
       </c>
     </row>
@@ -38384,7 +38378,7 @@
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>human being</t>
         </is>
       </c>
       <c r="M717" t="inlineStr">
@@ -39698,7 +39692,7 @@
       </c>
       <c r="M794" t="inlineStr">
         <is>
-          <t>A human or collection of humans that occupies a housing unit by storing their possessions there and habitually sleeping there thereby participating in the realization of its residence function.</t>
+          <t>A human or collection of humans that occupies a housing unit by storing their possessions there and habitually sleeping there thereby participating in the realization of that housing unit's residence function.</t>
         </is>
       </c>
     </row>
@@ -39749,7 +39743,7 @@
       </c>
       <c r="M797" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
@@ -39812,296 +39806,296 @@
       </c>
       <c r="M801" t="inlineStr">
         <is>
-          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
+          <t>b is a role means: b is a realizable entity and b exists because there is some single bearer that is in some special physical, social, or institutional set of circumstances in which this bearer does not have to beand b is not such that, if it ceases to exist, then the physical make-up of the bearer is thereby changed.</t>
         </is>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
+          <t>BCIO:015070</t>
         </is>
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>interpersonal role</t>
         </is>
       </c>
       <c r="M802" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+          <t>A role relating to personal relationships or association between an individual and other individuals, including kinship relations, romantic, business, and social interactions.</t>
         </is>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>BCIO:015084</t>
+          <t>BCIO:015108</t>
         </is>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>preschool student role</t>
+          <t>parental role</t>
         </is>
       </c>
       <c r="M803" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by  currently learning at an initial level of organised instruction, primarily to familiarise the bearer to the school-type environment.</t>
+          <t>An interpersonal role that is realised through a process of promoting and supporting the physical, emotional, social, and intellectual development of a child from infancy to adulthood.</t>
         </is>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
-        </is>
-      </c>
-      <c r="H804" t="inlineStr">
-        <is>
-          <t>school student role</t>
+          <t>OBI:0000093</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>patient role</t>
         </is>
       </c>
       <c r="M804" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+          <t>A role which inheres in a person and is realized by being under the care of a physician or health care provider.</t>
         </is>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:015080</t>
         </is>
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t>trainee role</t>
+          <t>outpatient role</t>
         </is>
       </c>
       <c r="M805" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+          <t>A patient role which inheres in a person and is realized by coming to a healthcare facility for diagnosis or treatment but not being admitted for an overnight stay.</t>
         </is>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>BCIO:010085</t>
+          <t>BCIO:015079</t>
         </is>
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>informal education student role</t>
+          <t>inpatient role</t>
         </is>
       </c>
       <c r="M806" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
+          <t>A patient role which inheres in a person and is realized by being under the care of a physician or health care provider and being admitted to a hospital or equivalent facility.</t>
         </is>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>BCIO:010088</t>
-        </is>
-      </c>
-      <c r="H807" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
+          <t>BCIO:015078</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>organisational role</t>
         </is>
       </c>
       <c r="M807" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
+          <t>A role which inheres in a person and is realised by performing the activities deemed appropriate for that particular role as specified in the organisation rules.</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>BCIO:010092</t>
-        </is>
-      </c>
-      <c r="I808" t="inlineStr">
-        <is>
-          <t>doctoral student role</t>
+          <t>BCIO:006081</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>personal role</t>
         </is>
       </c>
       <c r="M808" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
+          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
         </is>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>BCIO:010090</t>
-        </is>
-      </c>
-      <c r="I809" t="inlineStr">
-        <is>
-          <t>graduate student role</t>
+          <t>BCIO:010084</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="M809" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
+          <t>A personal role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:015084</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
         <is>
-          <t>undergraduate student role</t>
+          <t>preschool student role</t>
         </is>
       </c>
       <c r="M810" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
+          <t>A student or trainee role realised by  currently learning at an initial level of organised instruction, primarily to familiarise the bearer to the school-type environment.</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
+          <t>BCIO:010086</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
         <is>
-          <t>masters student role</t>
+          <t>school student role</t>
         </is>
       </c>
       <c r="M811" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a masters degree.</t>
+          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
         </is>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>BCIO:015070</t>
-        </is>
-      </c>
-      <c r="G812" t="inlineStr">
-        <is>
-          <t>interpersonal role</t>
+          <t>BCIO:010087</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>trainee role</t>
         </is>
       </c>
       <c r="M812" t="inlineStr">
         <is>
-          <t>A role relating to personal relationships or association between an individual and other individuals, including kinship relations, romantic, business, and social interactions.</t>
+          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>BCIO:015108</t>
-        </is>
-      </c>
-      <c r="H813" t="inlineStr">
-        <is>
-          <t>parental role</t>
+          <t>BCIO:010085</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>informal education student role</t>
         </is>
       </c>
       <c r="M813" t="inlineStr">
         <is>
-          <t>An interpersonal role that is realised through a process of promoting and supporting the physical, emotional, social, and intellectual development of a child from infancy to adulthood.</t>
+          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>OBI:0000093</t>
-        </is>
-      </c>
-      <c r="G814" t="inlineStr">
-        <is>
-          <t>patient role</t>
+          <t>BCIO:010088</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="M814" t="inlineStr">
         <is>
-          <t>a role which inheres in a person and is realized by the process of being under the care of a physician or health care provider</t>
+          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
         </is>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>BCIO:015080</t>
-        </is>
-      </c>
-      <c r="H815" t="inlineStr">
-        <is>
-          <t>outpatient role</t>
+          <t>BCIO:010092</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>doctoral student role</t>
         </is>
       </c>
       <c r="M815" t="inlineStr">
         <is>
-          <t>A patient role which inheres in a person and is realized by coming to a healthcare facility for diagnosis or treatment but not being admitted for an overnight stay.</t>
+          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>BCIO:015079</t>
-        </is>
-      </c>
-      <c r="H816" t="inlineStr">
-        <is>
-          <t>inpatient role</t>
+          <t>BCIO:010090</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>graduate student role</t>
         </is>
       </c>
       <c r="M816" t="inlineStr">
         <is>
-          <t>A patient role which inheres in a person and is realized by being under the care of a physician or health care provider and being admitted to a hospital or equivalent facility.</t>
+          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>BCIO:015078</t>
-        </is>
-      </c>
-      <c r="G817" t="inlineStr">
-        <is>
-          <t>organisational role</t>
+          <t>BCIO:010089</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>undergraduate student role</t>
         </is>
       </c>
       <c r="M817" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by performing the activities deemed appropriate for that particular role as specified in the organisation rules.</t>
+          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>BCIO:006081</t>
-        </is>
-      </c>
-      <c r="G818" t="inlineStr">
-        <is>
-          <t>personal role</t>
+          <t>BCIO:010091</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>masters student role</t>
         </is>
       </c>
       <c r="M818" t="inlineStr">
         <is>
-          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
+          <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
     </row>
@@ -40179,14 +40173,14 @@
           <t>BCIO:015077</t>
         </is>
       </c>
-      <c r="G823" t="inlineStr">
+      <c r="H823" t="inlineStr">
         <is>
           <t>caregiving role</t>
         </is>
       </c>
       <c r="M823" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by the person assuming responsibility for the physical and emotional needs of another who has difficulties with self care.</t>
+          <t>A personal role which inheres in a person and is realised by the person assuming responsibility for the physical and emotional needs of another who has difficulties with self care.</t>
         </is>
       </c>
     </row>
@@ -40504,7 +40498,7 @@
       </c>
       <c r="M842" t="inlineStr">
         <is>
-          <t>A cognitive representation of themselves by a person or group.</t>
+          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
         </is>
       </c>
     </row>
@@ -41813,7 +41807,7 @@
       </c>
       <c r="M919" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
+          <t>A process in which at least one bodily component of an organsim participates.</t>
         </is>
       </c>
     </row>
@@ -42357,7 +42351,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>A reference to a place on the Earth, by its name or by its geographical location.</t>
+          <t>A reference to a place on the Earth, by its name or by its geographical location</t>
         </is>
       </c>
     </row>
@@ -42442,7 +42436,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of water.</t>
+          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of wate</t>
         </is>
       </c>
     </row>
@@ -42527,7 +42521,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>An area in which grasses (Graminae) are a significant component of the vegetation.</t>
+          <t>An area in which grasses (Graminae) are a significant component of the vegetation</t>
         </is>
       </c>
     </row>
@@ -42578,7 +42572,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>An area with a high density of trees. A small forest may be called a wood.</t>
+          <t>An area with a high density of trees. A small forest may be called a wood</t>
         </is>
       </c>
     </row>
@@ -43107,153 +43101,153 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OMRSE:00000063</t>
+          <t>BCIO:026051</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>hospital facility</t>
+          <t>psychiatric facility</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>A facility that is run by a hospital organization, such as emergency departments, outpatient clinics and rehabilitation and is the bearer of a hospital function</t>
+          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OMRSE:00000114</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>emergency department facility</t>
+          <t>BCIO:026017</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>care home facility</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
+          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:026015</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>hospital outpatient clinic facility</t>
+          <t>BCIO:026019</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>community healthcare facility</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
+          <t>A clinic providing healthcare services to people in a certain area</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:026051</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>psychiatric facility</t>
+          <t>BCIO:026020</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>community outpatient clinic facility</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
+          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:026017</t>
+          <t>PDRO:0000074</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>care home facility</t>
+          <t>pharmacy facility</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
+          <t>Un établissement de santé qui a pour fonction d'entreposer, préparer, distribuer et surveiller l'utilisation des médicaments parmi les patients d'une zone géographique donnée ou suivis dans une organisation de soin donnée.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:026019</t>
+          <t>BCIO:026016</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>community healthcare facility</t>
+          <t>doctor-led primary care facility</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>A clinic providing healthcare services to people in a certain area</t>
+          <t>A healthcare facility led by doctors.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:026020</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>community outpatient clinic facility</t>
+          <t>OMRSE:00000063</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>hospital facility</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
+          <t>A facility that is run by a hospital organization, such as emergency departments, outpatient clinics and rehabilitation and is the bearer of a hospital function</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PDRO:0000074</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>pharmacy facility</t>
+          <t>OMRSE:00000114</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>emergency department facility</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization.</t>
+          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:026016</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>doctor-led primary care facility</t>
+          <t>BCIO:026015</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>hospital outpatient clinic facility</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>A healthcare facility led by doctors.</t>
+          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
         </is>
       </c>
     </row>
@@ -43729,7 +43723,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
@@ -44176,7 +44170,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
@@ -44222,7 +44216,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>human being</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -44375,7 +44369,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>organisation</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -44392,12 +44386,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>characteristic</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
@@ -44409,7 +44403,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>realizable entity</t>
+          <t>realizable</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -44438,170 +44432,170 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
+          <t>BCIO:006081</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>personal role</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
+          <t>BCIO:010084</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>school student role</t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+          <t>A personal role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>trainee role</t>
+          <t>BCIO:010086</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>school student role</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:010085</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>informal education student role</t>
+          <t>BCIO:010087</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>trainee role</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
+          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:010088</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
+          <t>BCIO:010085</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>informal education student role</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
+          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:010092</t>
+          <t>BCIO:010088</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>doctoral student role</t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
+          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:010090</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>graduate student role</t>
+          <t>BCIO:010092</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>doctoral student role</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
+          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>undergraduate student role</t>
+          <t>BCIO:010090</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>graduate student role</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
+          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>masters student role</t>
+          <t>BCIO:010089</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>undergraduate student role</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a masters degree.</t>
+          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:006081</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>personal role</t>
+          <t>BCIO:010091</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>masters student role</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
+          <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
     </row>
@@ -46998,7 +46992,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47055,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>human being</t>
+          <t>person</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -48171,7 +48165,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organsim participates.</t>
+          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
     </row>
